--- a/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_R2.xlsx
+++ b/ROSA_vitaSPEC/Results/test_pretraitements/SEC/ratio.alpha.beta/Resultats_ratio.alpha.beta_moy_R2.xlsx
@@ -451,49 +451,49 @@
         <v>0</v>
       </c>
       <c r="C2">
-        <v>0.008138815107534114</v>
+        <v>0.008138816378843727</v>
       </c>
       <c r="D2">
-        <v>0.03280661593605605</v>
+        <v>0.03280661916515504</v>
       </c>
       <c r="E2">
-        <v>0.06166163975988481</v>
+        <v>0.06166164428635479</v>
       </c>
       <c r="F2">
-        <v>0.09611430256490872</v>
+        <v>0.0961143062855051</v>
       </c>
       <c r="G2">
-        <v>0.127673390178658</v>
+        <v>0.1276733969380234</v>
       </c>
       <c r="H2">
-        <v>0.2090297194691594</v>
+        <v>0.2090297286911528</v>
       </c>
       <c r="I2">
-        <v>0.2450600611652051</v>
+        <v>0.245060070945969</v>
       </c>
       <c r="J2">
-        <v>0.3457678584179134</v>
+        <v>0.3457678645357258</v>
       </c>
       <c r="K2">
-        <v>0.3954915436963259</v>
+        <v>0.3954915487062521</v>
       </c>
       <c r="L2">
-        <v>0.4441368507423509</v>
+        <v>0.4441368574445433</v>
       </c>
       <c r="M2">
-        <v>0.5681273185846811</v>
+        <v>0.5681273283191447</v>
       </c>
       <c r="N2">
-        <v>0.6167007922060335</v>
+        <v>0.616700802934101</v>
       </c>
       <c r="O2">
-        <v>0.7072648915167024</v>
+        <v>0.7072649073306851</v>
       </c>
       <c r="P2">
-        <v>0.7816020577559278</v>
+        <v>0.7816020728138882</v>
       </c>
       <c r="Q2">
-        <v>0.7985423554551586</v>
+        <v>0.7985423696568925</v>
       </c>
     </row>
     <row r="3">
@@ -506,49 +506,49 @@
         <v>0</v>
       </c>
       <c r="C3">
-        <v>0.04137761724573641</v>
+        <v>0.04137761749353752</v>
       </c>
       <c r="D3">
-        <v>0.06492630786531117</v>
+        <v>0.06492630582959091</v>
       </c>
       <c r="E3">
-        <v>0.347181219848841</v>
+        <v>0.3471812194314163</v>
       </c>
       <c r="F3">
-        <v>0.3876377273084176</v>
+        <v>0.387637763867535</v>
       </c>
       <c r="G3">
-        <v>0.472015704723236</v>
+        <v>0.4720157195704139</v>
       </c>
       <c r="H3">
-        <v>0.5085023214787454</v>
+        <v>0.5085023196923026</v>
       </c>
       <c r="I3">
-        <v>0.5996408004458869</v>
+        <v>0.5996407913786816</v>
       </c>
       <c r="J3">
-        <v>0.6597872335807951</v>
+        <v>0.6597872270948009</v>
       </c>
       <c r="K3">
-        <v>0.70191265135343</v>
+        <v>0.7019126536083624</v>
       </c>
       <c r="L3">
-        <v>0.7435181144991281</v>
+        <v>0.7435181219602736</v>
       </c>
       <c r="M3">
-        <v>0.7659309557772922</v>
+        <v>0.7659309699783289</v>
       </c>
       <c r="N3">
-        <v>0.8002326119954608</v>
+        <v>0.8002326455755756</v>
       </c>
       <c r="O3">
-        <v>0.8345596377482658</v>
+        <v>0.8345596869589085</v>
       </c>
       <c r="P3">
-        <v>0.872790209623343</v>
+        <v>0.8727902790727322</v>
       </c>
       <c r="Q3">
-        <v>0.8908678431743652</v>
+        <v>0.8908679091916551</v>
       </c>
     </row>
     <row r="4">
@@ -561,49 +561,49 @@
         <v>0</v>
       </c>
       <c r="C4">
-        <v>0.007836597040745796</v>
+        <v>0.007836598183330934</v>
       </c>
       <c r="D4">
-        <v>0.01969763205080866</v>
+        <v>0.01969763314190942</v>
       </c>
       <c r="E4">
-        <v>0.04796567742957791</v>
+        <v>0.04796567557116604</v>
       </c>
       <c r="F4">
-        <v>0.06244627774416867</v>
+        <v>0.0624462697517999</v>
       </c>
       <c r="G4">
-        <v>0.1679381878370249</v>
+        <v>0.1679381963898224</v>
       </c>
       <c r="H4">
-        <v>0.2750088810985736</v>
+        <v>0.2750088918580434</v>
       </c>
       <c r="I4">
-        <v>0.404787255112401</v>
+        <v>0.4047872643501246</v>
       </c>
       <c r="J4">
-        <v>0.4722291631621839</v>
+        <v>0.4722291630723522</v>
       </c>
       <c r="K4">
-        <v>0.4931689460571317</v>
+        <v>0.4931689553452527</v>
       </c>
       <c r="L4">
-        <v>0.5911180222895676</v>
+        <v>0.5911180356419949</v>
       </c>
       <c r="M4">
-        <v>0.667604568027278</v>
+        <v>0.6676045843330116</v>
       </c>
       <c r="N4">
-        <v>0.7251575505221248</v>
+        <v>0.7251575624594176</v>
       </c>
       <c r="O4">
-        <v>0.7624873591658264</v>
+        <v>0.7624873714281184</v>
       </c>
       <c r="P4">
-        <v>0.7803904229769627</v>
+        <v>0.7803904344668828</v>
       </c>
       <c r="Q4">
-        <v>0.7960870349088087</v>
+        <v>0.796087049675839</v>
       </c>
     </row>
     <row r="5">
@@ -616,49 +616,49 @@
         <v>0</v>
       </c>
       <c r="C5">
-        <v>0.01980383558280785</v>
+        <v>0.01980383721271695</v>
       </c>
       <c r="D5">
-        <v>0.06176560679326371</v>
+        <v>0.06176561004242076</v>
       </c>
       <c r="E5">
-        <v>0.09841116670826255</v>
+        <v>0.09841116809166817</v>
       </c>
       <c r="F5">
-        <v>0.3324852816599347</v>
+        <v>0.3324852891178945</v>
       </c>
       <c r="G5">
-        <v>0.4133579315652824</v>
+        <v>0.4133579416681802</v>
       </c>
       <c r="H5">
-        <v>0.5621447977868761</v>
+        <v>0.5621448035970593</v>
       </c>
       <c r="I5">
-        <v>0.6025505795127939</v>
+        <v>0.6025505896656332</v>
       </c>
       <c r="J5">
-        <v>0.6598277901795893</v>
+        <v>0.6598278055245608</v>
       </c>
       <c r="K5">
-        <v>0.695193620180115</v>
+        <v>0.6951936371792709</v>
       </c>
       <c r="L5">
-        <v>0.7235825108055167</v>
+        <v>0.723582527718563</v>
       </c>
       <c r="M5">
-        <v>0.7615058148598371</v>
+        <v>0.7615058404137802</v>
       </c>
       <c r="N5">
-        <v>0.7806387379458956</v>
+        <v>0.7806387666620767</v>
       </c>
       <c r="O5">
-        <v>0.8024717832610795</v>
+        <v>0.8024718166315599</v>
       </c>
       <c r="P5">
-        <v>0.8166707638154656</v>
+        <v>0.81667080280388</v>
       </c>
       <c r="Q5">
-        <v>0.839040291310185</v>
+        <v>0.8390403387586943</v>
       </c>
     </row>
     <row r="6">
@@ -671,49 +671,49 @@
         <v>0</v>
       </c>
       <c r="C6">
-        <v>0.01753722337279118</v>
+        <v>0.01753722507073807</v>
       </c>
       <c r="D6">
-        <v>0.04840475005249478</v>
+        <v>0.04840475502893571</v>
       </c>
       <c r="E6">
-        <v>0.09723254352825483</v>
+        <v>0.09723254424850181</v>
       </c>
       <c r="F6">
-        <v>0.36845316144311</v>
+        <v>0.3684531734748679</v>
       </c>
       <c r="G6">
-        <v>0.4321599094740276</v>
+        <v>0.4321599140246225</v>
       </c>
       <c r="H6">
-        <v>0.5552510091836036</v>
+        <v>0.5552510340865662</v>
       </c>
       <c r="I6">
-        <v>0.592615942512674</v>
+        <v>0.5926159548283441</v>
       </c>
       <c r="J6">
-        <v>0.6608032818749004</v>
+        <v>0.6608032946863663</v>
       </c>
       <c r="K6">
-        <v>0.6998668380629514</v>
+        <v>0.6998668507704493</v>
       </c>
       <c r="L6">
-        <v>0.7206095183040799</v>
+        <v>0.7206095301076481</v>
       </c>
       <c r="M6">
-        <v>0.7555295465643258</v>
+        <v>0.7555295640424837</v>
       </c>
       <c r="N6">
-        <v>0.779399100499542</v>
+        <v>0.7793991185331042</v>
       </c>
       <c r="O6">
-        <v>0.8018987643096041</v>
+        <v>0.8018987786440162</v>
       </c>
       <c r="P6">
-        <v>0.8173332274557632</v>
+        <v>0.8173332533505238</v>
       </c>
       <c r="Q6">
-        <v>0.8382870502874693</v>
+        <v>0.83828708108142</v>
       </c>
     </row>
     <row r="7">
@@ -726,49 +726,49 @@
         <v>0</v>
       </c>
       <c r="C7">
-        <v>0.008149247996915188</v>
+        <v>0.00814924913292292</v>
       </c>
       <c r="D7">
-        <v>0.02038637635081386</v>
+        <v>0.02038637756494877</v>
       </c>
       <c r="E7">
-        <v>0.04030798391421497</v>
+        <v>0.04030798432777372</v>
       </c>
       <c r="F7">
-        <v>0.07712077350222069</v>
+        <v>0.077120787246864</v>
       </c>
       <c r="G7">
-        <v>0.1033712297207263</v>
+        <v>0.1033712333529294</v>
       </c>
       <c r="H7">
-        <v>0.2144341459995576</v>
+        <v>0.2144341540317277</v>
       </c>
       <c r="I7">
-        <v>0.3080133592890911</v>
+        <v>0.3080133714900384</v>
       </c>
       <c r="J7">
-        <v>0.4129143808596254</v>
+        <v>0.412914394562613</v>
       </c>
       <c r="K7">
-        <v>0.503471633765276</v>
+        <v>0.5034716416298755</v>
       </c>
       <c r="L7">
-        <v>0.5188418738118062</v>
+        <v>0.5188418673442265</v>
       </c>
       <c r="M7">
-        <v>0.6306418935227012</v>
+        <v>0.6306419131264001</v>
       </c>
       <c r="N7">
-        <v>0.7277815083957963</v>
+        <v>0.727781521330819</v>
       </c>
       <c r="O7">
-        <v>0.7542253129958099</v>
+        <v>0.7542253117487371</v>
       </c>
       <c r="P7">
-        <v>0.777767694526997</v>
+        <v>0.7777677076154089</v>
       </c>
       <c r="Q7">
-        <v>0.7948606455122003</v>
+        <v>0.7948606571858733</v>
       </c>
     </row>
     <row r="8">
@@ -781,49 +781,49 @@
         <v>0</v>
       </c>
       <c r="C8">
-        <v>0.01154569860863619</v>
+        <v>0.01154570002005184</v>
       </c>
       <c r="D8">
-        <v>0.02005680848314739</v>
+        <v>0.02005680992079129</v>
       </c>
       <c r="E8">
-        <v>0.04760606973304826</v>
+        <v>0.04760607086747637</v>
       </c>
       <c r="F8">
-        <v>0.145268556092087</v>
+        <v>0.1452685564544163</v>
       </c>
       <c r="G8">
-        <v>0.2176686626158466</v>
+        <v>0.2176686676764201</v>
       </c>
       <c r="H8">
-        <v>0.3158692120900987</v>
+        <v>0.315869221863457</v>
       </c>
       <c r="I8">
-        <v>0.3788879374044499</v>
+        <v>0.3788879493484105</v>
       </c>
       <c r="J8">
-        <v>0.4911978413626983</v>
+        <v>0.4911978555777065</v>
       </c>
       <c r="K8">
-        <v>0.5350423856345181</v>
+        <v>0.5350424007647379</v>
       </c>
       <c r="L8">
-        <v>0.6700157910879154</v>
+        <v>0.6700158098296349</v>
       </c>
       <c r="M8">
-        <v>0.7054500226195228</v>
+        <v>0.7054500370411823</v>
       </c>
       <c r="N8">
-        <v>0.7466154075976629</v>
+        <v>0.7466154189897243</v>
       </c>
       <c r="O8">
-        <v>0.7696693015106494</v>
+        <v>0.7696693153858415</v>
       </c>
       <c r="P8">
-        <v>0.7848539975877291</v>
+        <v>0.7848540130161497</v>
       </c>
       <c r="Q8">
-        <v>0.7992992862658402</v>
+        <v>0.7992993009441538</v>
       </c>
     </row>
     <row r="9">
@@ -836,49 +836,49 @@
         <v>0</v>
       </c>
       <c r="C9">
-        <v>0.01152313456493093</v>
+        <v>0.01152313597622745</v>
       </c>
       <c r="D9">
-        <v>0.01991239859640215</v>
+        <v>0.0199124000272185</v>
       </c>
       <c r="E9">
-        <v>0.04486120388122394</v>
+        <v>0.04486120530462478</v>
       </c>
       <c r="F9">
-        <v>0.129367219507963</v>
+        <v>0.1293672205366246</v>
       </c>
       <c r="G9">
-        <v>0.1919422206922079</v>
+        <v>0.1919422261268358</v>
       </c>
       <c r="H9">
-        <v>0.2782630034682333</v>
+        <v>0.278263013309767</v>
       </c>
       <c r="I9">
-        <v>0.3312803443308547</v>
+        <v>0.3312803559074275</v>
       </c>
       <c r="J9">
-        <v>0.4326303986671299</v>
+        <v>0.4326304115163677</v>
       </c>
       <c r="K9">
-        <v>0.4641845967556236</v>
+        <v>0.4641846113731956</v>
       </c>
       <c r="L9">
-        <v>0.6091709331912263</v>
+        <v>0.6091709488167492</v>
       </c>
       <c r="M9">
-        <v>0.6515293836318006</v>
+        <v>0.6515293959182529</v>
       </c>
       <c r="N9">
-        <v>0.6693354897140324</v>
+        <v>0.6693355050684169</v>
       </c>
       <c r="O9">
-        <v>0.6925158353804789</v>
+        <v>0.6925158512248333</v>
       </c>
       <c r="P9">
-        <v>0.7078322818994096</v>
+        <v>0.7078322949711298</v>
       </c>
       <c r="Q9">
-        <v>0.7340895419990188</v>
+        <v>0.7340895616280507</v>
       </c>
     </row>
     <row r="10">
@@ -891,49 +891,49 @@
         <v>0</v>
       </c>
       <c r="C10">
-        <v>0.01152168948984955</v>
+        <v>0.01152169090087463</v>
       </c>
       <c r="D10">
-        <v>0.01991093147459011</v>
+        <v>0.01991093290408785</v>
       </c>
       <c r="E10">
-        <v>0.04487432521330792</v>
+        <v>0.04487432664457025</v>
       </c>
       <c r="F10">
-        <v>0.1287421374526238</v>
+        <v>0.128742138480307</v>
       </c>
       <c r="G10">
-        <v>0.190550449043809</v>
+        <v>0.1905504545528882</v>
       </c>
       <c r="H10">
-        <v>0.2765967362649516</v>
+        <v>0.2765967462463196</v>
       </c>
       <c r="I10">
-        <v>0.3284805653222311</v>
+        <v>0.3284805770469246</v>
       </c>
       <c r="J10">
-        <v>0.428068693009273</v>
+        <v>0.4280687059570141</v>
       </c>
       <c r="K10">
-        <v>0.4587118092132828</v>
+        <v>0.4587118240715273</v>
       </c>
       <c r="L10">
-        <v>0.6017659980616903</v>
+        <v>0.6017660132382143</v>
       </c>
       <c r="M10">
-        <v>0.6423419911025521</v>
+        <v>0.6423420043085013</v>
       </c>
       <c r="N10">
-        <v>0.661932625463724</v>
+        <v>0.6619326434372346</v>
       </c>
       <c r="O10">
-        <v>0.683731050313124</v>
+        <v>0.6837310725851794</v>
       </c>
       <c r="P10">
-        <v>0.6959202369884018</v>
+        <v>0.6959202514779111</v>
       </c>
       <c r="Q10">
-        <v>0.7239230875084359</v>
+        <v>0.7239231088952689</v>
       </c>
     </row>
     <row r="11">
@@ -946,49 +946,49 @@
         <v>0</v>
       </c>
       <c r="C11">
-        <v>0.01152875063315162</v>
+        <v>0.0115287520439199</v>
       </c>
       <c r="D11">
-        <v>0.01994316756941572</v>
+        <v>0.01994316899822191</v>
       </c>
       <c r="E11">
-        <v>0.04519165179630469</v>
+        <v>0.04519165319663399</v>
       </c>
       <c r="F11">
-        <v>0.1283375192472423</v>
+        <v>0.1283375204235976</v>
       </c>
       <c r="G11">
-        <v>0.1891380719154154</v>
+        <v>0.1891380774438471</v>
       </c>
       <c r="H11">
-        <v>0.2745861152790905</v>
+        <v>0.274586125242427</v>
       </c>
       <c r="I11">
-        <v>0.3284341747438898</v>
+        <v>0.3284341866443424</v>
       </c>
       <c r="J11">
-        <v>0.4321981951388422</v>
+        <v>0.432198208747036</v>
       </c>
       <c r="K11">
-        <v>0.4667272134623552</v>
+        <v>0.4667272288918931</v>
       </c>
       <c r="L11">
-        <v>0.606368998152762</v>
+        <v>0.6063690150907672</v>
       </c>
       <c r="M11">
-        <v>0.6473398587196182</v>
+        <v>0.6473398730522562</v>
       </c>
       <c r="N11">
-        <v>0.6693744127476636</v>
+        <v>0.6693744284343314</v>
       </c>
       <c r="O11">
-        <v>0.6908687831951945</v>
+        <v>0.690868800577365</v>
       </c>
       <c r="P11">
-        <v>0.7038732612611136</v>
+        <v>0.7038732774417157</v>
       </c>
       <c r="Q11">
-        <v>0.7234204418344667</v>
+        <v>0.7234204585128627</v>
       </c>
     </row>
     <row r="12">
@@ -1001,49 +1001,49 @@
         <v>0</v>
       </c>
       <c r="C12">
-        <v>0.02054951250612636</v>
+        <v>0.02054951423303808</v>
       </c>
       <c r="D12">
-        <v>0.06198495345680577</v>
+        <v>0.06198495694425143</v>
       </c>
       <c r="E12">
-        <v>0.09725879831196549</v>
+        <v>0.09725879908196222</v>
       </c>
       <c r="F12">
-        <v>0.2785444640271529</v>
+        <v>0.278544474608293</v>
       </c>
       <c r="G12">
-        <v>0.4179340282554229</v>
+        <v>0.4179340270405195</v>
       </c>
       <c r="H12">
-        <v>0.5057786907945625</v>
+        <v>0.505778694439472</v>
       </c>
       <c r="I12">
-        <v>0.600989989845832</v>
+        <v>0.6009900001585996</v>
       </c>
       <c r="J12">
-        <v>0.6679626166691924</v>
+        <v>0.6679626353397303</v>
       </c>
       <c r="K12">
-        <v>0.7024941222736564</v>
+        <v>0.7024941408940117</v>
       </c>
       <c r="L12">
-        <v>0.7279096002396117</v>
+        <v>0.7279096195636254</v>
       </c>
       <c r="M12">
-        <v>0.7692896786244847</v>
+        <v>0.7692897097203741</v>
       </c>
       <c r="N12">
-        <v>0.7892920497217275</v>
+        <v>0.7892920845092621</v>
       </c>
       <c r="O12">
-        <v>0.8106182018788173</v>
+        <v>0.8106182389610713</v>
       </c>
       <c r="P12">
-        <v>0.8252525092752536</v>
+        <v>0.8252525468523763</v>
       </c>
       <c r="Q12">
-        <v>0.848870212844166</v>
+        <v>0.8488702580740447</v>
       </c>
     </row>
     <row r="13">
@@ -1056,49 +1056,49 @@
         <v>0</v>
       </c>
       <c r="C13">
-        <v>0.02451161151884673</v>
+        <v>0.02451161326606277</v>
       </c>
       <c r="D13">
-        <v>0.09309033201405537</v>
+        <v>0.09309033625645191</v>
       </c>
       <c r="E13">
-        <v>0.1593498724788895</v>
+        <v>0.1593498689080114</v>
       </c>
       <c r="F13">
-        <v>0.2520000001507794</v>
+        <v>0.2519999925047266</v>
       </c>
       <c r="G13">
-        <v>0.3368146268315027</v>
+        <v>0.3368146219760011</v>
       </c>
       <c r="H13">
-        <v>0.4651637963406741</v>
+        <v>0.4651637969872956</v>
       </c>
       <c r="I13">
-        <v>0.5625095202106618</v>
+        <v>0.5625095219932277</v>
       </c>
       <c r="J13">
-        <v>0.6107832328017928</v>
+        <v>0.6107832288561106</v>
       </c>
       <c r="K13">
-        <v>0.6707984818876908</v>
+        <v>0.6707984913446494</v>
       </c>
       <c r="L13">
-        <v>0.7189025793934112</v>
+        <v>0.7189026012567903</v>
       </c>
       <c r="M13">
-        <v>0.7418392070501914</v>
+        <v>0.7418392332521067</v>
       </c>
       <c r="N13">
-        <v>0.7749095030426005</v>
+        <v>0.7749095409296418</v>
       </c>
       <c r="O13">
-        <v>0.7849186505555674</v>
+        <v>0.7849186916614023</v>
       </c>
       <c r="P13">
-        <v>0.806605249120987</v>
+        <v>0.8066053003397614</v>
       </c>
       <c r="Q13">
-        <v>0.8237738442266441</v>
+        <v>0.8237738996395952</v>
       </c>
     </row>
     <row r="14">
@@ -1111,49 +1111,49 @@
         <v>0</v>
       </c>
       <c r="C14">
-        <v>0.008142429455032074</v>
+        <v>0.008142430590888372</v>
       </c>
       <c r="D14">
-        <v>0.0203278333571667</v>
+        <v>0.02032783456628739</v>
       </c>
       <c r="E14">
-        <v>0.03904364454562903</v>
+        <v>0.03904364516000502</v>
       </c>
       <c r="F14">
-        <v>0.07255859246028118</v>
+        <v>0.0725586051763335</v>
       </c>
       <c r="G14">
-        <v>0.09593468645420489</v>
+        <v>0.09593469005002164</v>
       </c>
       <c r="H14">
-        <v>0.1943365561156274</v>
+        <v>0.1943365638302634</v>
       </c>
       <c r="I14">
-        <v>0.2765734059963531</v>
+        <v>0.2765734178601212</v>
       </c>
       <c r="J14">
-        <v>0.3662826853506194</v>
+        <v>0.3662826988364297</v>
       </c>
       <c r="K14">
-        <v>0.4552215937015605</v>
+        <v>0.4552216068342729</v>
       </c>
       <c r="L14">
-        <v>0.5545527765393345</v>
+        <v>0.5545522992311258</v>
       </c>
       <c r="M14">
-        <v>0.5691642387851588</v>
+        <v>0.5691642254841736</v>
       </c>
       <c r="N14">
-        <v>0.6736252607475056</v>
+        <v>0.6736252752799436</v>
       </c>
       <c r="O14">
-        <v>0.689820048121309</v>
+        <v>0.689820063550733</v>
       </c>
       <c r="P14">
-        <v>0.7210721326116291</v>
+        <v>0.7210721523794066</v>
       </c>
       <c r="Q14">
-        <v>0.7342878136826749</v>
+        <v>0.7342878301449791</v>
       </c>
     </row>
     <row r="15">
@@ -1166,49 +1166,49 @@
         <v>0</v>
       </c>
       <c r="C15">
-        <v>0.008138881981781143</v>
+        <v>0.008138883117755458</v>
       </c>
       <c r="D15">
-        <v>0.02030998180629817</v>
+        <v>0.02030998301550369</v>
       </c>
       <c r="E15">
-        <v>0.03868885261154609</v>
+        <v>0.03868885331316652</v>
       </c>
       <c r="F15">
-        <v>0.07128465461445277</v>
+        <v>0.07128466715063464</v>
       </c>
       <c r="G15">
-        <v>0.09372040560118811</v>
+        <v>0.09372040948089522</v>
       </c>
       <c r="H15">
-        <v>0.1887039205189883</v>
+        <v>0.1887039286057274</v>
       </c>
       <c r="I15">
-        <v>0.2689540771657162</v>
+        <v>0.268954089470593</v>
       </c>
       <c r="J15">
-        <v>0.3561684374270981</v>
+        <v>0.3561684514700475</v>
       </c>
       <c r="K15">
-        <v>0.4453301254786658</v>
+        <v>0.4453301405036429</v>
       </c>
       <c r="L15">
-        <v>0.535602642428441</v>
+        <v>0.5356032093004748</v>
       </c>
       <c r="M15">
-        <v>0.5534872442316797</v>
+        <v>0.5534872773521748</v>
       </c>
       <c r="N15">
-        <v>0.6578961297762784</v>
+        <v>0.6578961444076359</v>
       </c>
       <c r="O15">
-        <v>0.6732652893878891</v>
+        <v>0.6732653046861895</v>
       </c>
       <c r="P15">
-        <v>0.7026465377819764</v>
+        <v>0.7026465578716611</v>
       </c>
       <c r="Q15">
-        <v>0.7179214947100769</v>
+        <v>0.7179215103628126</v>
       </c>
     </row>
     <row r="16">
@@ -1221,49 +1221,49 @@
         <v>0</v>
       </c>
       <c r="C16">
-        <v>0.008134698502606619</v>
+        <v>0.008134699638664644</v>
       </c>
       <c r="D16">
-        <v>0.02029008036855962</v>
+        <v>0.0202900815775342</v>
       </c>
       <c r="E16">
-        <v>0.03837913643096091</v>
+        <v>0.03837913719260322</v>
       </c>
       <c r="F16">
-        <v>0.07048984393610824</v>
+        <v>0.07048985639569327</v>
       </c>
       <c r="G16">
-        <v>0.09251151693064164</v>
+        <v>0.09251152094286552</v>
       </c>
       <c r="H16">
-        <v>0.1874397842780077</v>
+        <v>0.1874397923942496</v>
       </c>
       <c r="I16">
-        <v>0.2680541659306787</v>
+        <v>0.2680541783951518</v>
       </c>
       <c r="J16">
-        <v>0.3522770336667643</v>
+        <v>0.3522770475620103</v>
       </c>
       <c r="K16">
-        <v>0.4396241709988072</v>
+        <v>0.43962418076584</v>
       </c>
       <c r="L16">
-        <v>0.4586775775626446</v>
+        <v>0.4586775141632822</v>
       </c>
       <c r="M16">
-        <v>0.5483307266261324</v>
+        <v>0.548330745725754</v>
       </c>
       <c r="N16">
-        <v>0.6528417981149985</v>
+        <v>0.6528418117332865</v>
       </c>
       <c r="O16">
-        <v>0.6701710093570457</v>
+        <v>0.6701710241909316</v>
       </c>
       <c r="P16">
-        <v>0.7023307802662739</v>
+        <v>0.7023308002057105</v>
       </c>
       <c r="Q16">
-        <v>0.7183394340480568</v>
+        <v>0.7183394498339353</v>
       </c>
     </row>
     <row r="17">
@@ -1276,49 +1276,49 @@
         <v>0</v>
       </c>
       <c r="C17">
-        <v>0.008129854822600757</v>
+        <v>0.008129855958634247</v>
       </c>
       <c r="D17">
-        <v>0.02028317956374293</v>
+        <v>0.02028318077342561</v>
       </c>
       <c r="E17">
-        <v>0.0382282193647262</v>
+        <v>0.03822822016130689</v>
       </c>
       <c r="F17">
-        <v>0.07019630189046988</v>
+        <v>0.07019631423317996</v>
       </c>
       <c r="G17">
-        <v>0.09133205362736319</v>
+        <v>0.0913320581828434</v>
       </c>
       <c r="H17">
-        <v>0.1841457011554151</v>
+        <v>0.1841457093605702</v>
       </c>
       <c r="I17">
-        <v>0.2640051365502498</v>
+        <v>0.2640051491735163</v>
       </c>
       <c r="J17">
-        <v>0.3413023645963188</v>
+        <v>0.3413023787455269</v>
       </c>
       <c r="K17">
-        <v>0.4271411338631886</v>
+        <v>0.4271411505516305</v>
       </c>
       <c r="L17">
-        <v>0.4717468540902103</v>
+        <v>0.4717472566454913</v>
       </c>
       <c r="M17">
-        <v>0.5327219003772694</v>
+        <v>0.5327219208105183</v>
       </c>
       <c r="N17">
-        <v>0.6278545308394519</v>
+        <v>0.6278545453824299</v>
       </c>
       <c r="O17">
-        <v>0.6506021069098337</v>
+        <v>0.650602123319471</v>
       </c>
       <c r="P17">
-        <v>0.6871381589790835</v>
+        <v>0.6871381810156758</v>
       </c>
       <c r="Q17">
-        <v>0.7061548063468653</v>
+        <v>0.7061548242030254</v>
       </c>
     </row>
     <row r="18">
@@ -1331,49 +1331,49 @@
         <v>0</v>
       </c>
       <c r="C18">
-        <v>0.02049618379123497</v>
+        <v>0.02049618552035037</v>
       </c>
       <c r="D18">
-        <v>0.06155000667198485</v>
+        <v>0.06155001016209949</v>
       </c>
       <c r="E18">
-        <v>0.0964311393421754</v>
+        <v>0.09643114049219415</v>
       </c>
       <c r="F18">
-        <v>0.2957576384512525</v>
+        <v>0.2957576493524379</v>
       </c>
       <c r="G18">
-        <v>0.4042241232695819</v>
+        <v>0.4042241325150776</v>
       </c>
       <c r="H18">
-        <v>0.5504453125755322</v>
+        <v>0.550445322391375</v>
       </c>
       <c r="I18">
-        <v>0.5900848865286905</v>
+        <v>0.5900848984072249</v>
       </c>
       <c r="J18">
-        <v>0.6842508909295104</v>
+        <v>0.68425090756225</v>
       </c>
       <c r="K18">
-        <v>0.7142333728204222</v>
+        <v>0.7142333912305717</v>
       </c>
       <c r="L18">
-        <v>0.7285815909858129</v>
+        <v>0.7285816093583527</v>
       </c>
       <c r="M18">
-        <v>0.7666022211853074</v>
+        <v>0.7666022491573851</v>
       </c>
       <c r="N18">
-        <v>0.7865679476892999</v>
+        <v>0.7865679776496654</v>
       </c>
       <c r="O18">
-        <v>0.8075789423114824</v>
+        <v>0.8075789749663009</v>
       </c>
       <c r="P18">
-        <v>0.823145335387876</v>
+        <v>0.8231453723348453</v>
       </c>
       <c r="Q18">
-        <v>0.8467303167219143</v>
+        <v>0.8467303629566155</v>
       </c>
     </row>
     <row r="19">
@@ -1386,49 +1386,49 @@
         <v>0</v>
       </c>
       <c r="C19">
-        <v>0.01816923019189354</v>
+        <v>0.01816923199686338</v>
       </c>
       <c r="D19">
-        <v>0.04794434664392333</v>
+        <v>0.04794435190533586</v>
       </c>
       <c r="E19">
-        <v>0.09543007111450508</v>
+        <v>0.09543007175404417</v>
       </c>
       <c r="F19">
-        <v>0.3394435911999218</v>
+        <v>0.3394436076553268</v>
       </c>
       <c r="G19">
-        <v>0.4329701911952726</v>
+        <v>0.4329701986769675</v>
       </c>
       <c r="H19">
-        <v>0.5468937765377913</v>
+        <v>0.5468937949780345</v>
       </c>
       <c r="I19">
-        <v>0.5909165726633974</v>
+        <v>0.5909165907100383</v>
       </c>
       <c r="J19">
-        <v>0.6496140023884673</v>
+        <v>0.6496140156118638</v>
       </c>
       <c r="K19">
-        <v>0.6896756896535274</v>
+        <v>0.6896757037523527</v>
       </c>
       <c r="L19">
-        <v>0.717117836206512</v>
+        <v>0.7171178487271288</v>
       </c>
       <c r="M19">
-        <v>0.7585600298529962</v>
+        <v>0.7585600472491445</v>
       </c>
       <c r="N19">
-        <v>0.7828720426978436</v>
+        <v>0.7828720610790829</v>
       </c>
       <c r="O19">
-        <v>0.8128434267375773</v>
+        <v>0.8128434500621877</v>
       </c>
       <c r="P19">
-        <v>0.8234682956652017</v>
+        <v>0.8234683214583952</v>
       </c>
       <c r="Q19">
-        <v>0.8435564617653012</v>
+        <v>0.8435564912511343</v>
       </c>
     </row>
     <row r="20">
@@ -1441,49 +1441,49 @@
         <v>0</v>
       </c>
       <c r="C20">
-        <v>0.01742502591444228</v>
+        <v>0.01742502771566479</v>
       </c>
       <c r="D20">
-        <v>0.04295361868756231</v>
+        <v>0.04295362488744359</v>
       </c>
       <c r="E20">
-        <v>0.1231932549234488</v>
+        <v>0.1231932545672068</v>
       </c>
       <c r="F20">
-        <v>0.2935912582754854</v>
+        <v>0.2935912661761897</v>
       </c>
       <c r="G20">
-        <v>0.4091344131401702</v>
+        <v>0.4091344201997317</v>
       </c>
       <c r="H20">
-        <v>0.5259094362877038</v>
+        <v>0.5259094308599366</v>
       </c>
       <c r="I20">
-        <v>0.5656702486145948</v>
+        <v>0.5656702489894037</v>
       </c>
       <c r="J20">
-        <v>0.6248712803400376</v>
+        <v>0.6248712927239646</v>
       </c>
       <c r="K20">
-        <v>0.6482744087250398</v>
+        <v>0.6482744214240167</v>
       </c>
       <c r="L20">
-        <v>0.6973765284668145</v>
+        <v>0.6973765386867218</v>
       </c>
       <c r="M20">
-        <v>0.7343334861291022</v>
+        <v>0.7343335010839277</v>
       </c>
       <c r="N20">
-        <v>0.7599303312899317</v>
+        <v>0.7599303504449209</v>
       </c>
       <c r="O20">
-        <v>0.7811983110573389</v>
+        <v>0.781198333177241</v>
       </c>
       <c r="P20">
-        <v>0.799336450346392</v>
+        <v>0.7993364773046915</v>
       </c>
       <c r="Q20">
-        <v>0.8154730278679643</v>
+        <v>0.8154730538416203</v>
       </c>
     </row>
     <row r="21">
@@ -1496,49 +1496,49 @@
         <v>0</v>
       </c>
       <c r="C21">
-        <v>0.04108935684331005</v>
+        <v>0.0410893571045492</v>
       </c>
       <c r="D21">
-        <v>0.06358032758058307</v>
+        <v>0.06358032592186624</v>
       </c>
       <c r="E21">
-        <v>0.3201253916289433</v>
+        <v>0.320125397667931</v>
       </c>
       <c r="F21">
-        <v>0.3567984317121768</v>
+        <v>0.3567984510001507</v>
       </c>
       <c r="G21">
-        <v>0.4353118094397266</v>
+        <v>0.4353118333696613</v>
       </c>
       <c r="H21">
-        <v>0.4817901778630234</v>
+        <v>0.4817901796627606</v>
       </c>
       <c r="I21">
-        <v>0.5834573040132247</v>
+        <v>0.5834573058116852</v>
       </c>
       <c r="J21">
-        <v>0.6645088639738472</v>
+        <v>0.6645088640471352</v>
       </c>
       <c r="K21">
-        <v>0.7048801194918639</v>
+        <v>0.7048801307107682</v>
       </c>
       <c r="L21">
-        <v>0.7504018787107722</v>
+        <v>0.7504019055377276</v>
       </c>
       <c r="M21">
-        <v>0.7798332493346543</v>
+        <v>0.7798332904504466</v>
       </c>
       <c r="N21">
-        <v>0.8062939827744005</v>
+        <v>0.8062940325913243</v>
       </c>
       <c r="O21">
-        <v>0.8362643481834461</v>
+        <v>0.8362644160516345</v>
       </c>
       <c r="P21">
-        <v>0.870205548531149</v>
+        <v>0.8702056388671924</v>
       </c>
       <c r="Q21">
-        <v>0.8900924890189605</v>
+        <v>0.8900925892396544</v>
       </c>
     </row>
     <row r="22">
@@ -1551,49 +1551,49 @@
         <v>0</v>
       </c>
       <c r="C22">
-        <v>0.04102667169539653</v>
+        <v>0.04102667192590381</v>
       </c>
       <c r="D22">
-        <v>0.06359150997037932</v>
+        <v>0.06359150821240822</v>
       </c>
       <c r="E22">
-        <v>0.318784099158906</v>
+        <v>0.3187841046611944</v>
       </c>
       <c r="F22">
-        <v>0.3543610566817569</v>
+        <v>0.3543610748857713</v>
       </c>
       <c r="G22">
-        <v>0.4267902890840075</v>
+        <v>0.4267903111147182</v>
       </c>
       <c r="H22">
-        <v>0.4692226270008075</v>
+        <v>0.4692226320205551</v>
       </c>
       <c r="I22">
-        <v>0.5708339342251443</v>
+        <v>0.5708339428465639</v>
       </c>
       <c r="J22">
-        <v>0.6426272872669806</v>
+        <v>0.6426272969987017</v>
       </c>
       <c r="K22">
-        <v>0.6905244355357132</v>
+        <v>0.6905244531541381</v>
       </c>
       <c r="L22">
-        <v>0.7374733085441871</v>
+        <v>0.7374733384251788</v>
       </c>
       <c r="M22">
-        <v>0.7798972321640226</v>
+        <v>0.7798972885570069</v>
       </c>
       <c r="N22">
-        <v>0.8115929748250653</v>
+        <v>0.8115930460966549</v>
       </c>
       <c r="O22">
-        <v>0.8440106584662517</v>
+        <v>0.844010745717495</v>
       </c>
       <c r="P22">
-        <v>0.8636842162647203</v>
+        <v>0.8636843098443054</v>
       </c>
       <c r="Q22">
-        <v>0.8802548337062048</v>
+        <v>0.8802549269230713</v>
       </c>
     </row>
     <row r="23">
@@ -1606,49 +1606,49 @@
         <v>0</v>
       </c>
       <c r="C23">
-        <v>0.02599067419987988</v>
+        <v>0.02599067460579307</v>
       </c>
       <c r="D23">
-        <v>0.1250768615259352</v>
+        <v>0.1250768871859902</v>
       </c>
       <c r="E23">
-        <v>0.240000806404908</v>
+        <v>0.2400008046141906</v>
       </c>
       <c r="F23">
-        <v>0.3218031678737291</v>
+        <v>0.3218031428670599</v>
       </c>
       <c r="G23">
-        <v>0.5402034937334093</v>
+        <v>0.5402034739234101</v>
       </c>
       <c r="H23">
-        <v>0.6274561829853995</v>
+        <v>0.6274561837416848</v>
       </c>
       <c r="I23">
-        <v>0.6821213281629086</v>
+        <v>0.68212134181132</v>
       </c>
       <c r="J23">
-        <v>0.741616366734773</v>
+        <v>0.7416164002344914</v>
       </c>
       <c r="K23">
-        <v>0.7708881097611017</v>
+        <v>0.7708881513243319</v>
       </c>
       <c r="L23">
-        <v>0.816847390297968</v>
+        <v>0.8168474400519566</v>
       </c>
       <c r="M23">
-        <v>0.8470927786087649</v>
+        <v>0.8470928583591051</v>
       </c>
       <c r="N23">
-        <v>0.8822534255278314</v>
+        <v>0.8822534735005072</v>
       </c>
       <c r="O23">
-        <v>0.8952594039181703</v>
+        <v>0.8952594417249347</v>
       </c>
       <c r="P23">
-        <v>0.9111800083870538</v>
+        <v>0.9111800344299541</v>
       </c>
       <c r="Q23">
-        <v>0.928464740122995</v>
+        <v>0.9284647390034414</v>
       </c>
     </row>
     <row r="24">
@@ -1661,49 +1661,49 @@
         <v>0</v>
       </c>
       <c r="C24">
-        <v>0.004024106045102505</v>
+        <v>0.004024107144069644</v>
       </c>
       <c r="D24">
-        <v>0.02386009143528012</v>
+        <v>0.02386009748906026</v>
       </c>
       <c r="E24">
-        <v>0.04077924193293503</v>
+        <v>0.04077924098102115</v>
       </c>
       <c r="F24">
-        <v>0.06930244464398294</v>
+        <v>0.06930242810113829</v>
       </c>
       <c r="G24">
-        <v>0.1040941899635768</v>
+        <v>0.1040941972189078</v>
       </c>
       <c r="H24">
-        <v>0.1668893751776583</v>
+        <v>0.1668893858889838</v>
       </c>
       <c r="I24">
-        <v>0.2163266336632435</v>
+        <v>0.2163266590360302</v>
       </c>
       <c r="J24">
-        <v>0.3903010081781513</v>
+        <v>0.390301036574852</v>
       </c>
       <c r="K24">
-        <v>0.5989974288689471</v>
+        <v>0.5989974729600898</v>
       </c>
       <c r="L24">
-        <v>0.658126669164246</v>
+        <v>0.6581267096358048</v>
       </c>
       <c r="M24">
-        <v>0.7087055116142482</v>
+        <v>0.7087055672887101</v>
       </c>
       <c r="N24">
-        <v>0.7738171140556058</v>
+        <v>0.7738171631505846</v>
       </c>
       <c r="O24">
-        <v>0.8289912654399119</v>
+        <v>0.8289913066878047</v>
       </c>
       <c r="P24">
-        <v>0.854054123225453</v>
+        <v>0.8540541619678452</v>
       </c>
       <c r="Q24">
-        <v>0.873831341956929</v>
+        <v>0.8738313777252641</v>
       </c>
     </row>
     <row r="25">
@@ -1716,49 +1716,49 @@
         <v>0</v>
       </c>
       <c r="C25">
-        <v>0.004309423043286409</v>
+        <v>0.00430942412420332</v>
       </c>
       <c r="D25">
-        <v>0.03237831125058521</v>
+        <v>0.03237831797249036</v>
       </c>
       <c r="E25">
-        <v>0.05585819661913649</v>
+        <v>0.0558581931244142</v>
       </c>
       <c r="F25">
-        <v>0.0911658690639281</v>
+        <v>0.09116585506849162</v>
       </c>
       <c r="G25">
-        <v>0.100538020179238</v>
+        <v>0.1005380178253785</v>
       </c>
       <c r="H25">
-        <v>0.1492382330199343</v>
+        <v>0.1492382391986273</v>
       </c>
       <c r="I25">
-        <v>0.1952794039534389</v>
+        <v>0.1952794106328104</v>
       </c>
       <c r="J25">
-        <v>0.4082462350904972</v>
+        <v>0.4082462603235556</v>
       </c>
       <c r="K25">
-        <v>0.4804746026009773</v>
+        <v>0.4804746272711581</v>
       </c>
       <c r="L25">
-        <v>0.6520414535918574</v>
+        <v>0.652041488385835</v>
       </c>
       <c r="M25">
-        <v>0.6808988619369847</v>
+        <v>0.6808989047902134</v>
       </c>
       <c r="N25">
-        <v>0.73885717335773</v>
+        <v>0.7388572328934278</v>
       </c>
       <c r="O25">
-        <v>0.7841730233447172</v>
+        <v>0.7841730735671151</v>
       </c>
       <c r="P25">
-        <v>0.8353257288558364</v>
+        <v>0.8353257717190313</v>
       </c>
       <c r="Q25">
-        <v>0.8545708535337754</v>
+        <v>0.8545708949592419</v>
       </c>
     </row>
     <row r="26">
@@ -1771,49 +1771,49 @@
         <v>0</v>
       </c>
       <c r="C26">
-        <v>0.004511575802238155</v>
+        <v>0.004511576833643005</v>
       </c>
       <c r="D26">
-        <v>0.04298657733523348</v>
+        <v>0.04298658338085715</v>
       </c>
       <c r="E26">
-        <v>0.05384606310758211</v>
+        <v>0.05384606471766085</v>
       </c>
       <c r="F26">
-        <v>0.09382877613019602</v>
+        <v>0.09382876764829096</v>
       </c>
       <c r="G26">
-        <v>0.1275644276607656</v>
+        <v>0.1275644327174422</v>
       </c>
       <c r="H26">
-        <v>0.1738278310711359</v>
+        <v>0.1738278405175451</v>
       </c>
       <c r="I26">
-        <v>0.3826207309866966</v>
+        <v>0.3826207481953139</v>
       </c>
       <c r="J26">
-        <v>0.5394091989830625</v>
+        <v>0.5394089778335281</v>
       </c>
       <c r="K26">
-        <v>0.596174050900568</v>
+        <v>0.596174074116529</v>
       </c>
       <c r="L26">
-        <v>0.6859949262647009</v>
+        <v>0.685994968880526</v>
       </c>
       <c r="M26">
-        <v>0.7334970128587366</v>
+        <v>0.7334970670812091</v>
       </c>
       <c r="N26">
-        <v>0.7997864529058215</v>
+        <v>0.7997865036922845</v>
       </c>
       <c r="O26">
-        <v>0.8323180962943092</v>
+        <v>0.8323181472716695</v>
       </c>
       <c r="P26">
-        <v>0.8514951305256984</v>
+        <v>0.8514951760588783</v>
       </c>
       <c r="Q26">
-        <v>0.8795196506347119</v>
+        <v>0.8795196937287958</v>
       </c>
     </row>
     <row r="27">
@@ -1826,49 +1826,49 @@
         <v>0</v>
       </c>
       <c r="C27">
-        <v>0.004468236546673943</v>
+        <v>0.004468237578039269</v>
       </c>
       <c r="D27">
-        <v>0.03994961915976381</v>
+        <v>0.03994962470386021</v>
       </c>
       <c r="E27">
-        <v>0.04933651284077079</v>
+        <v>0.04933651386674043</v>
       </c>
       <c r="F27">
-        <v>0.08122702694318107</v>
+        <v>0.08122701919031361</v>
       </c>
       <c r="G27">
-        <v>0.1063328784705342</v>
+        <v>0.1063328803850716</v>
       </c>
       <c r="H27">
-        <v>0.1359296249785293</v>
+        <v>0.1359296285729744</v>
       </c>
       <c r="I27">
-        <v>0.2654163157765536</v>
+        <v>0.2654163275351276</v>
       </c>
       <c r="J27">
-        <v>0.3840890470076562</v>
+        <v>0.38408881360331</v>
       </c>
       <c r="K27">
-        <v>0.4502150183085093</v>
+        <v>0.4502150401179883</v>
       </c>
       <c r="L27">
-        <v>0.5612329342567495</v>
+        <v>0.5612329739614842</v>
       </c>
       <c r="M27">
-        <v>0.5887808312085722</v>
+        <v>0.5887808727523092</v>
       </c>
       <c r="N27">
-        <v>0.6473118150927852</v>
+        <v>0.6473118760500416</v>
       </c>
       <c r="O27">
-        <v>0.6691240787142643</v>
+        <v>0.6691241615349673</v>
       </c>
       <c r="P27">
-        <v>0.6965298643550879</v>
+        <v>0.6965299417033157</v>
       </c>
       <c r="Q27">
-        <v>0.7141343423912969</v>
+        <v>0.7141344176503388</v>
       </c>
     </row>
     <row r="28">
@@ -1881,49 +1881,49 @@
         <v>0</v>
       </c>
       <c r="C28">
-        <v>0.00427159123711629</v>
+        <v>0.004271592318194073</v>
       </c>
       <c r="D28">
-        <v>0.03006462353989559</v>
+        <v>0.03006462981546087</v>
       </c>
       <c r="E28">
-        <v>0.0515814563677236</v>
+        <v>0.05158145299708194</v>
       </c>
       <c r="F28">
-        <v>0.07999651715970613</v>
+        <v>0.0799965049075646</v>
       </c>
       <c r="G28">
-        <v>0.08690281317591264</v>
+        <v>0.08690281087061091</v>
       </c>
       <c r="H28">
-        <v>0.1191872070461673</v>
+        <v>0.1191872095364341</v>
       </c>
       <c r="I28">
-        <v>0.1436130523595676</v>
+        <v>0.1436130545668242</v>
       </c>
       <c r="J28">
-        <v>0.2828716926810672</v>
+        <v>0.2828717075656733</v>
       </c>
       <c r="K28">
-        <v>0.3426432595422696</v>
+        <v>0.3426432752595795</v>
       </c>
       <c r="L28">
-        <v>0.5460620301653192</v>
+        <v>0.5460620748877322</v>
       </c>
       <c r="M28">
-        <v>0.5653670413906557</v>
+        <v>0.5653670857077797</v>
       </c>
       <c r="N28">
-        <v>0.5850188627355899</v>
+        <v>0.5850189082855568</v>
       </c>
       <c r="O28">
-        <v>0.6347106404948712</v>
+        <v>0.6347106961220819</v>
       </c>
       <c r="P28">
-        <v>0.6658325874848765</v>
+        <v>0.6658326535320984</v>
       </c>
       <c r="Q28">
-        <v>0.6934459024298216</v>
+        <v>0.6934459767434261</v>
       </c>
     </row>
     <row r="29">
@@ -1936,49 +1936,49 @@
         <v>0</v>
       </c>
       <c r="C29">
-        <v>0.004273917638383917</v>
+        <v>0.004273918719879033</v>
       </c>
       <c r="D29">
-        <v>0.03010160907394832</v>
+        <v>0.03010161535960287</v>
       </c>
       <c r="E29">
-        <v>0.05159401144055265</v>
+        <v>0.05159400811555015</v>
       </c>
       <c r="F29">
-        <v>0.08019840410814372</v>
+        <v>0.08019839204910761</v>
       </c>
       <c r="G29">
-        <v>0.08699328102900283</v>
+        <v>0.08699327854094652</v>
       </c>
       <c r="H29">
-        <v>0.1191538987768315</v>
+        <v>0.1191539009786237</v>
       </c>
       <c r="I29">
-        <v>0.1433390331107028</v>
+        <v>0.143339034705503</v>
       </c>
       <c r="J29">
-        <v>0.2795402238791156</v>
+        <v>0.279540238131869</v>
       </c>
       <c r="K29">
-        <v>0.3401080450516358</v>
+        <v>0.3401080601841195</v>
       </c>
       <c r="L29">
-        <v>0.5437818022109088</v>
+        <v>0.5437818473936509</v>
       </c>
       <c r="M29">
-        <v>0.5608692027986228</v>
+        <v>0.5608692470138718</v>
       </c>
       <c r="N29">
-        <v>0.5804525739369102</v>
+        <v>0.5804526185582011</v>
       </c>
       <c r="O29">
-        <v>0.6305071425737885</v>
+        <v>0.6305071953878209</v>
       </c>
       <c r="P29">
-        <v>0.6630349255363768</v>
+        <v>0.6630349890271954</v>
       </c>
       <c r="Q29">
-        <v>0.6904020418848849</v>
+        <v>0.690402116513739</v>
       </c>
     </row>
     <row r="30">
@@ -1991,49 +1991,49 @@
         <v>0</v>
       </c>
       <c r="C30">
-        <v>0.004268206225499505</v>
+        <v>0.004268207306704408</v>
       </c>
       <c r="D30">
-        <v>0.02979636164927768</v>
+        <v>0.02979636785598305</v>
       </c>
       <c r="E30">
-        <v>0.05109753088457525</v>
+        <v>0.05109752756434871</v>
       </c>
       <c r="F30">
-        <v>0.07890300042039222</v>
+        <v>0.07890298792932682</v>
       </c>
       <c r="G30">
-        <v>0.08583229403234871</v>
+        <v>0.08583229220560418</v>
       </c>
       <c r="H30">
-        <v>0.1170728819946687</v>
+        <v>0.1170728838830707</v>
       </c>
       <c r="I30">
-        <v>0.1401136556292656</v>
+        <v>0.1401136567711047</v>
       </c>
       <c r="J30">
-        <v>0.2733711188877879</v>
+        <v>0.2733711323353737</v>
       </c>
       <c r="K30">
-        <v>0.3355075430412497</v>
+        <v>0.3355075569707531</v>
       </c>
       <c r="L30">
-        <v>0.5374117908274798</v>
+        <v>0.5374118333819078</v>
       </c>
       <c r="M30">
-        <v>0.5538972245664731</v>
+        <v>0.5538972656355764</v>
       </c>
       <c r="N30">
-        <v>0.5719122784040479</v>
+        <v>0.5719123186880493</v>
       </c>
       <c r="O30">
-        <v>0.6238126752427025</v>
+        <v>0.6238127209598835</v>
       </c>
       <c r="P30">
-        <v>0.6587469206548447</v>
+        <v>0.6587469762022053</v>
       </c>
       <c r="Q30">
-        <v>0.6848813850821138</v>
+        <v>0.6848814517713655</v>
       </c>
     </row>
     <row r="31">
@@ -2046,49 +2046,49 @@
         <v>0</v>
       </c>
       <c r="C31">
-        <v>0.004258807347848559</v>
+        <v>0.004258808430639083</v>
       </c>
       <c r="D31">
-        <v>0.02934379951341792</v>
+        <v>0.02934380569500727</v>
       </c>
       <c r="E31">
-        <v>0.0503934328734551</v>
+        <v>0.05039342970641103</v>
       </c>
       <c r="F31">
-        <v>0.07691518712105905</v>
+        <v>0.0769151744224803</v>
       </c>
       <c r="G31">
-        <v>0.08421427205764365</v>
+        <v>0.08421427138748006</v>
       </c>
       <c r="H31">
-        <v>0.114026985842452</v>
+        <v>0.1140269879618679</v>
       </c>
       <c r="I31">
-        <v>0.1353526667220273</v>
+        <v>0.1353526682234568</v>
       </c>
       <c r="J31">
-        <v>0.2611393889681974</v>
+        <v>0.261139404370035</v>
       </c>
       <c r="K31">
-        <v>0.3265263738278679</v>
+        <v>0.3265263900469217</v>
       </c>
       <c r="L31">
-        <v>0.5290370001838085</v>
+        <v>0.529037043290304</v>
       </c>
       <c r="M31">
-        <v>0.5474317120404038</v>
+        <v>0.5474317540436207</v>
       </c>
       <c r="N31">
-        <v>0.5607312830481477</v>
+        <v>0.5607313223825836</v>
       </c>
       <c r="O31">
-        <v>0.6143459554952154</v>
+        <v>0.6143459920075394</v>
       </c>
       <c r="P31">
-        <v>0.6562354190144466</v>
+        <v>0.656235463210719</v>
       </c>
       <c r="Q31">
-        <v>0.6804861684906053</v>
+        <v>0.6804862249399048</v>
       </c>
     </row>
     <row r="32">
@@ -2101,49 +2101,49 @@
         <v>0</v>
       </c>
       <c r="C32">
-        <v>0.004281808004088505</v>
+        <v>0.004281809084451527</v>
       </c>
       <c r="D32">
-        <v>0.0306274095508392</v>
+        <v>0.03062741590693097</v>
       </c>
       <c r="E32">
-        <v>0.05259677804785934</v>
+        <v>0.05259677459226864</v>
       </c>
       <c r="F32">
-        <v>0.08248288943629511</v>
+        <v>0.0824828772315398</v>
       </c>
       <c r="G32">
-        <v>0.08958234779747898</v>
+        <v>0.08958234469076076</v>
       </c>
       <c r="H32">
-        <v>0.1242276730807036</v>
+        <v>0.1242276761554583</v>
       </c>
       <c r="I32">
-        <v>0.1515284979596904</v>
+        <v>0.1515285010217821</v>
       </c>
       <c r="J32">
-        <v>0.2977650097215064</v>
+        <v>0.2977650261164141</v>
       </c>
       <c r="K32">
-        <v>0.3565492897941709</v>
+        <v>0.3565493079096306</v>
       </c>
       <c r="L32">
-        <v>0.5604155880405496</v>
+        <v>0.5604156369961133</v>
       </c>
       <c r="M32">
-        <v>0.5791346332331774</v>
+        <v>0.5791346837673783</v>
       </c>
       <c r="N32">
-        <v>0.6031117926669733</v>
+        <v>0.6031118494779277</v>
       </c>
       <c r="O32">
-        <v>0.6519502413852558</v>
+        <v>0.651950308765619</v>
       </c>
       <c r="P32">
-        <v>0.688737395498674</v>
+        <v>0.6887374721287549</v>
       </c>
       <c r="Q32">
-        <v>0.7233641070110091</v>
+        <v>0.7233641867724411</v>
       </c>
     </row>
     <row r="33">
@@ -2156,49 +2156,49 @@
         <v>0</v>
       </c>
       <c r="C33">
-        <v>0.004279040750468366</v>
+        <v>0.004279041831223962</v>
       </c>
       <c r="D33">
-        <v>0.0304478541674057</v>
+        <v>0.03044786050457415</v>
       </c>
       <c r="E33">
-        <v>0.05224369130174744</v>
+        <v>0.05224368789573541</v>
       </c>
       <c r="F33">
-        <v>0.08160178238463744</v>
+        <v>0.08160177026922477</v>
       </c>
       <c r="G33">
-        <v>0.08858940037286478</v>
+        <v>0.08858939754377371</v>
       </c>
       <c r="H33">
-        <v>0.1222752070789668</v>
+        <v>0.1222752100356809</v>
       </c>
       <c r="I33">
-        <v>0.14837028136149</v>
+        <v>0.1483702843113324</v>
       </c>
       <c r="J33">
-        <v>0.2905990387131731</v>
+        <v>0.2905990550890089</v>
       </c>
       <c r="K33">
-        <v>0.3490345774403918</v>
+        <v>0.3490345954182198</v>
       </c>
       <c r="L33">
-        <v>0.5561912363114165</v>
+        <v>0.5561912839759777</v>
       </c>
       <c r="M33">
-        <v>0.5755772847046028</v>
+        <v>0.5755773330128279</v>
       </c>
       <c r="N33">
-        <v>0.5987897507791696</v>
+        <v>0.5987898027550098</v>
       </c>
       <c r="O33">
-        <v>0.6451283697934758</v>
+        <v>0.6451284288388714</v>
       </c>
       <c r="P33">
-        <v>0.6819351328332548</v>
+        <v>0.6819352014089606</v>
       </c>
       <c r="Q33">
-        <v>0.7166668820957353</v>
+        <v>0.7166669555967435</v>
       </c>
     </row>
     <row r="34">
@@ -2211,49 +2211,49 @@
         <v>0</v>
       </c>
       <c r="C34">
-        <v>0.004277046288847175</v>
+        <v>0.004277047369760756</v>
       </c>
       <c r="D34">
-        <v>0.03030904233090737</v>
+        <v>0.03030904863490913</v>
       </c>
       <c r="E34">
-        <v>0.05194539605419002</v>
+        <v>0.05194539266866405</v>
       </c>
       <c r="F34">
-        <v>0.08093158931686573</v>
+        <v>0.08093157722973454</v>
       </c>
       <c r="G34">
-        <v>0.08783328489683473</v>
+        <v>0.08783328220651587</v>
       </c>
       <c r="H34">
-        <v>0.1207537701050124</v>
+        <v>0.1207537727870529</v>
       </c>
       <c r="I34">
-        <v>0.1457783501640263</v>
+        <v>0.1457783527294263</v>
       </c>
       <c r="J34">
-        <v>0.2834114636922581</v>
+        <v>0.2834114791554312</v>
       </c>
       <c r="K34">
-        <v>0.341587181666728</v>
+        <v>0.3415871984813447</v>
       </c>
       <c r="L34">
-        <v>0.5536917589081003</v>
+        <v>0.5536918040780715</v>
       </c>
       <c r="M34">
-        <v>0.5726595186460037</v>
+        <v>0.5726595639045983</v>
       </c>
       <c r="N34">
-        <v>0.5945898773107957</v>
+        <v>0.5945899251219384</v>
       </c>
       <c r="O34">
-        <v>0.6391793787743935</v>
+        <v>0.6391794342275061</v>
       </c>
       <c r="P34">
-        <v>0.6764744230681816</v>
+        <v>0.6764744910878662</v>
       </c>
       <c r="Q34">
-        <v>0.7070456869797423</v>
+        <v>0.707045762553919</v>
       </c>
     </row>
     <row r="35">
@@ -2266,49 +2266,49 @@
         <v>0</v>
       </c>
       <c r="C35">
-        <v>0.004276411745970154</v>
+        <v>0.004276412826814235</v>
       </c>
       <c r="D35">
-        <v>0.03022108980082738</v>
+        <v>0.03022109606562673</v>
       </c>
       <c r="E35">
-        <v>0.05175125402239389</v>
+        <v>0.0517512506362332</v>
       </c>
       <c r="F35">
-        <v>0.08055150956896973</v>
+        <v>0.08055149738975276</v>
       </c>
       <c r="G35">
-        <v>0.08744542453443982</v>
+        <v>0.0874454219772639</v>
       </c>
       <c r="H35">
-        <v>0.1199948009518418</v>
+        <v>0.119994803329224</v>
       </c>
       <c r="I35">
-        <v>0.1443712916351968</v>
+        <v>0.1443712937440695</v>
       </c>
       <c r="J35">
-        <v>0.2791228996948314</v>
+        <v>0.2791229143576505</v>
       </c>
       <c r="K35">
-        <v>0.3369810026194464</v>
+        <v>0.3369810185787774</v>
       </c>
       <c r="L35">
-        <v>0.5489795080566745</v>
+        <v>0.5489795519108479</v>
       </c>
       <c r="M35">
-        <v>0.5670508026014007</v>
+        <v>0.5670508461853734</v>
       </c>
       <c r="N35">
-        <v>0.5868757909362229</v>
+        <v>0.5868758361592432</v>
       </c>
       <c r="O35">
-        <v>0.6287809584353442</v>
+        <v>0.6287810116212382</v>
       </c>
       <c r="P35">
-        <v>0.6650759205489915</v>
+        <v>0.6650759873717165</v>
       </c>
       <c r="Q35">
-        <v>0.69230549287569</v>
+        <v>0.6923055691594415</v>
       </c>
     </row>
     <row r="36">
@@ -2321,49 +2321,49 @@
         <v>0</v>
       </c>
       <c r="C36">
-        <v>0.004270031210824476</v>
+        <v>0.004270032294000026</v>
       </c>
       <c r="D36">
-        <v>0.02978600407566256</v>
+        <v>0.02978601031187267</v>
       </c>
       <c r="E36">
-        <v>0.05089102508455934</v>
+        <v>0.05089102192244932</v>
       </c>
       <c r="F36">
-        <v>0.07894240222782611</v>
+        <v>0.07894239020214255</v>
       </c>
       <c r="G36">
-        <v>0.08578786515929493</v>
+        <v>0.08578786364084001</v>
       </c>
       <c r="H36">
-        <v>0.1166548522380634</v>
+        <v>0.1166548543161202</v>
       </c>
       <c r="I36">
-        <v>0.1387440168570634</v>
+        <v>0.1387440182659314</v>
       </c>
       <c r="J36">
-        <v>0.2619429160337043</v>
+        <v>0.2619429315473202</v>
       </c>
       <c r="K36">
-        <v>0.3238516686392932</v>
+        <v>0.3238516861478403</v>
       </c>
       <c r="L36">
-        <v>0.5258190191226004</v>
+        <v>0.5258190654021164</v>
       </c>
       <c r="M36">
-        <v>0.5511301573220877</v>
+        <v>0.5511301996073552</v>
       </c>
       <c r="N36">
-        <v>0.5662900793522945</v>
+        <v>0.5662901151941826</v>
       </c>
       <c r="O36">
-        <v>0.6062322621761156</v>
+        <v>0.6062323020358142</v>
       </c>
       <c r="P36">
-        <v>0.6508113784029386</v>
+        <v>0.6508114247466208</v>
       </c>
       <c r="Q36">
-        <v>0.6789380197197723</v>
+        <v>0.6789380769778992</v>
       </c>
     </row>
     <row r="37">
@@ -2376,49 +2376,49 @@
         <v>0</v>
       </c>
       <c r="C37">
-        <v>0.00806850257902969</v>
+        <v>0.008068503050782772</v>
       </c>
       <c r="D37">
-        <v>0.1299520233770577</v>
+        <v>0.1299520522229674</v>
       </c>
       <c r="E37">
-        <v>0.157684127344583</v>
+        <v>0.1576841453325604</v>
       </c>
       <c r="F37">
-        <v>0.2332926386011963</v>
+        <v>0.2332926584217072</v>
       </c>
       <c r="G37">
-        <v>0.4019382314400769</v>
+        <v>0.4019383265870372</v>
       </c>
       <c r="H37">
-        <v>0.4859101272766783</v>
+        <v>0.4859102578814926</v>
       </c>
       <c r="I37">
-        <v>0.6060942901924251</v>
+        <v>0.6060944171653637</v>
       </c>
       <c r="J37">
-        <v>0.6329827956448845</v>
+        <v>0.632982897511122</v>
       </c>
       <c r="K37">
-        <v>0.6777493466683268</v>
+        <v>0.6777494272974857</v>
       </c>
       <c r="L37">
-        <v>0.7404422358242251</v>
+        <v>0.7404423198653708</v>
       </c>
       <c r="M37">
-        <v>0.7785396303703038</v>
+        <v>0.7785397359376438</v>
       </c>
       <c r="N37">
-        <v>0.8154559217278898</v>
+        <v>0.8154560385617422</v>
       </c>
       <c r="O37">
-        <v>0.8445691323386892</v>
+        <v>0.8445692697413277</v>
       </c>
       <c r="P37">
-        <v>0.8629194607867747</v>
+        <v>0.8629195964297609</v>
       </c>
       <c r="Q37">
-        <v>0.8728603160935637</v>
+        <v>0.8728604469462036</v>
       </c>
     </row>
     <row r="38">
@@ -2431,49 +2431,49 @@
         <v>0</v>
       </c>
       <c r="C38">
-        <v>0.005412661314427969</v>
+        <v>0.005412662072316166</v>
       </c>
       <c r="D38">
-        <v>0.07481637422829035</v>
+        <v>0.07481640198071526</v>
       </c>
       <c r="E38">
-        <v>0.09896349267256033</v>
+        <v>0.09896349936012494</v>
       </c>
       <c r="F38">
-        <v>0.232243530513833</v>
+        <v>0.2322435501311958</v>
       </c>
       <c r="G38">
-        <v>0.4116130667095645</v>
+        <v>0.4116131021641578</v>
       </c>
       <c r="H38">
-        <v>0.4826707302957779</v>
+        <v>0.4826707877709331</v>
       </c>
       <c r="I38">
-        <v>0.5271093084280798</v>
+        <v>0.5271093746153153</v>
       </c>
       <c r="J38">
-        <v>0.5718440245545888</v>
+        <v>0.5718440947656831</v>
       </c>
       <c r="K38">
-        <v>0.6217196373230044</v>
+        <v>0.6217197036565502</v>
       </c>
       <c r="L38">
-        <v>0.6513176745363918</v>
+        <v>0.651317743260722</v>
       </c>
       <c r="M38">
-        <v>0.6985399350656422</v>
+        <v>0.6985399909332831</v>
       </c>
       <c r="N38">
-        <v>0.7348916465808258</v>
+        <v>0.7348916970841604</v>
       </c>
       <c r="O38">
-        <v>0.7752336431307504</v>
+        <v>0.7752337011835937</v>
       </c>
       <c r="P38">
-        <v>0.8117324443501638</v>
+        <v>0.8117324975480872</v>
       </c>
       <c r="Q38">
-        <v>0.8332971542273826</v>
+        <v>0.8332972011076688</v>
       </c>
     </row>
     <row r="39">
@@ -2486,49 +2486,49 @@
         <v>0</v>
       </c>
       <c r="C39">
-        <v>0.005529065439923819</v>
+        <v>0.005529066213672551</v>
       </c>
       <c r="D39">
-        <v>0.0738217420430014</v>
+        <v>0.07382175958031889</v>
       </c>
       <c r="E39">
-        <v>0.09284542237286431</v>
+        <v>0.09284542664639717</v>
       </c>
       <c r="F39">
-        <v>0.197261889210572</v>
+        <v>0.1972618927582312</v>
       </c>
       <c r="G39">
-        <v>0.3198389143792864</v>
+        <v>0.3198389217655571</v>
       </c>
       <c r="H39">
-        <v>0.3921755545519374</v>
+        <v>0.3921755797520612</v>
       </c>
       <c r="I39">
-        <v>0.4827829506650637</v>
+        <v>0.4827829870321022</v>
       </c>
       <c r="J39">
-        <v>0.5257897676835794</v>
+        <v>0.5257898178279485</v>
       </c>
       <c r="K39">
-        <v>0.5957670686250967</v>
+        <v>0.5957671281819847</v>
       </c>
       <c r="L39">
-        <v>0.617507158847668</v>
+        <v>0.6175072208563654</v>
       </c>
       <c r="M39">
-        <v>0.6515406186533415</v>
+        <v>0.6515406672903632</v>
       </c>
       <c r="N39">
-        <v>0.6926819377512371</v>
+        <v>0.6926819978291355</v>
       </c>
       <c r="O39">
-        <v>0.7380339595328205</v>
+        <v>0.7380340290631997</v>
       </c>
       <c r="P39">
-        <v>0.7706795906777266</v>
+        <v>0.7706796608745325</v>
       </c>
       <c r="Q39">
-        <v>0.8058580786669516</v>
+        <v>0.8058581396861555</v>
       </c>
     </row>
     <row r="40">
@@ -2541,49 +2541,49 @@
         <v>0</v>
       </c>
       <c r="C40">
-        <v>0.01395523663929743</v>
+        <v>0.01395523531135912</v>
       </c>
       <c r="D40">
-        <v>0.04782731656612071</v>
+        <v>0.0478273174361461</v>
       </c>
       <c r="E40">
-        <v>0.2218584575686143</v>
+        <v>0.2218584684752264</v>
       </c>
       <c r="F40">
-        <v>0.2463732798457554</v>
+        <v>0.2463732689685401</v>
       </c>
       <c r="G40">
-        <v>0.4380918496702108</v>
+        <v>0.4380919212214814</v>
       </c>
       <c r="H40">
-        <v>0.5212860475259926</v>
+        <v>0.5212860913022304</v>
       </c>
       <c r="I40">
-        <v>0.5780405635720323</v>
+        <v>0.5780406636657051</v>
       </c>
       <c r="J40">
-        <v>0.6602622029370734</v>
+        <v>0.6602622838090401</v>
       </c>
       <c r="K40">
-        <v>0.7076498547021299</v>
+        <v>0.7076498996189273</v>
       </c>
       <c r="L40">
-        <v>0.7582031083283017</v>
+        <v>0.7582031754505079</v>
       </c>
       <c r="M40">
-        <v>0.7804776868764784</v>
+        <v>0.7804777476136064</v>
       </c>
       <c r="N40">
-        <v>0.8056414282989681</v>
+        <v>0.8056415015500624</v>
       </c>
       <c r="O40">
-        <v>0.8278370941426234</v>
+        <v>0.827837151170171</v>
       </c>
       <c r="P40">
-        <v>0.8480156663934481</v>
+        <v>0.8480157352366681</v>
       </c>
       <c r="Q40">
-        <v>0.8695398912896223</v>
+        <v>0.869539938309819</v>
       </c>
     </row>
     <row r="41">
@@ -2596,49 +2596,49 @@
         <v>0</v>
       </c>
       <c r="C41">
-        <v>0.05147895604695329</v>
+        <v>0.05147895770218902</v>
       </c>
       <c r="D41">
-        <v>0.2123324763072013</v>
+        <v>0.2123324850028042</v>
       </c>
       <c r="E41">
-        <v>0.3529476338755499</v>
+        <v>0.3529476298549304</v>
       </c>
       <c r="F41">
-        <v>0.4248654367957254</v>
+        <v>0.424865443588283</v>
       </c>
       <c r="G41">
-        <v>0.5168561306056348</v>
+        <v>0.5168561218956027</v>
       </c>
       <c r="H41">
-        <v>0.5617223327239577</v>
+        <v>0.5617223217482522</v>
       </c>
       <c r="I41">
-        <v>0.6370135316239076</v>
+        <v>0.6370135390451258</v>
       </c>
       <c r="J41">
-        <v>0.6757191304422365</v>
+        <v>0.6757191403109383</v>
       </c>
       <c r="K41">
-        <v>0.7108674019558909</v>
+        <v>0.7108674153878181</v>
       </c>
       <c r="L41">
-        <v>0.7524667813365058</v>
+        <v>0.7524668204106436</v>
       </c>
       <c r="M41">
-        <v>0.779099644199388</v>
+        <v>0.7790996584797745</v>
       </c>
       <c r="N41">
-        <v>0.816357834897663</v>
+        <v>0.8163578436817535</v>
       </c>
       <c r="O41">
-        <v>0.8414946047440314</v>
+        <v>0.8414946110221341</v>
       </c>
       <c r="P41">
-        <v>0.8640375127989137</v>
+        <v>0.8640375193992568</v>
       </c>
       <c r="Q41">
-        <v>0.8834465646411541</v>
+        <v>0.8834465731103471</v>
       </c>
     </row>
     <row r="42">
@@ -2651,49 +2651,49 @@
         <v>0</v>
       </c>
       <c r="C42">
-        <v>0.04607334055647216</v>
+        <v>0.04607334060272938</v>
       </c>
       <c r="D42">
-        <v>0.09430810554446689</v>
+        <v>0.09430809879708368</v>
       </c>
       <c r="E42">
-        <v>0.3186900947615909</v>
+        <v>0.3186901154899296</v>
       </c>
       <c r="F42">
-        <v>0.4544330926787558</v>
+        <v>0.4544331039420632</v>
       </c>
       <c r="G42">
-        <v>0.5691128220095524</v>
+        <v>0.5691128049382221</v>
       </c>
       <c r="H42">
-        <v>0.6384772140733237</v>
+        <v>0.6384772001669744</v>
       </c>
       <c r="I42">
-        <v>0.704627052934955</v>
+        <v>0.704627049854947</v>
       </c>
       <c r="J42">
-        <v>0.7472863569662325</v>
+        <v>0.7472863179475857</v>
       </c>
       <c r="K42">
-        <v>0.7702350386163898</v>
+        <v>0.7702350293585272</v>
       </c>
       <c r="L42">
-        <v>0.8051239897275936</v>
+        <v>0.8051239883523134</v>
       </c>
       <c r="M42">
-        <v>0.8323197029175523</v>
+        <v>0.8323197080693876</v>
       </c>
       <c r="N42">
-        <v>0.8648101344012777</v>
+        <v>0.8648101436845548</v>
       </c>
       <c r="O42">
-        <v>0.8912150546165747</v>
+        <v>0.8912150669548208</v>
       </c>
       <c r="P42">
-        <v>0.8995085057956776</v>
+        <v>0.899508519533556</v>
       </c>
       <c r="Q42">
-        <v>0.91740578922838</v>
+        <v>0.9174058101403552</v>
       </c>
     </row>
     <row r="43">
@@ -2706,49 +2706,49 @@
         <v>0</v>
       </c>
       <c r="C43">
-        <v>0.02850711830779029</v>
+        <v>0.02850711963277908</v>
       </c>
       <c r="D43">
-        <v>0.1328664925923085</v>
+        <v>0.1328664986789091</v>
       </c>
       <c r="E43">
-        <v>0.3107462117928</v>
+        <v>0.3107462028356432</v>
       </c>
       <c r="F43">
-        <v>0.4424440709110021</v>
+        <v>0.4424440583699688</v>
       </c>
       <c r="G43">
-        <v>0.5434672393310999</v>
+        <v>0.5434672260481387</v>
       </c>
       <c r="H43">
-        <v>0.5829974480750847</v>
+        <v>0.5829974392044115</v>
       </c>
       <c r="I43">
-        <v>0.6436607103637738</v>
+        <v>0.6436607052337502</v>
       </c>
       <c r="J43">
-        <v>0.6960758872351608</v>
+        <v>0.6960758874129858</v>
       </c>
       <c r="K43">
-        <v>0.7528593865477613</v>
+        <v>0.7528593903883128</v>
       </c>
       <c r="L43">
-        <v>0.7950415290543877</v>
+        <v>0.7950415374858527</v>
       </c>
       <c r="M43">
-        <v>0.8251969668390378</v>
+        <v>0.8251969816094915</v>
       </c>
       <c r="N43">
-        <v>0.8527149875534512</v>
+        <v>0.8527150047104944</v>
       </c>
       <c r="O43">
-        <v>0.869104366587707</v>
+        <v>0.8691043828590637</v>
       </c>
       <c r="P43">
-        <v>0.8851051816225664</v>
+        <v>0.8851051986042753</v>
       </c>
       <c r="Q43">
-        <v>0.8986912103710879</v>
+        <v>0.8986912279495142</v>
       </c>
     </row>
   </sheetData>
